--- a/Preguntar_impactos/Preguntar_si_se_calculan.xlsx
+++ b/Preguntar_impactos/Preguntar_si_se_calculan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PDE\DEMO\Preguntar_impactos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3424512-6314-4E96-8A57-FA4959241177}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84B784F6-69CD-4D7C-86DE-D021D95FF081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="18">
   <si>
     <t>Zona de fondeo y espera exterior</t>
   </si>
@@ -81,6 +81,18 @@
   </si>
   <si>
     <t>Modos de fallo / Modos de parada</t>
+  </si>
+  <si>
+    <t>Pantalán</t>
+  </si>
+  <si>
+    <t>Duque de alba</t>
+  </si>
+  <si>
+    <t>Boya / monoboya</t>
+  </si>
+  <si>
+    <t>Rampa Ro-Ro</t>
   </si>
 </sst>
 </file>
@@ -622,13 +634,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BEC1923-1B83-4CAE-813F-14B40C51E688}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="43.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -721,11 +733,119 @@
         <v>3</v>
       </c>
     </row>
+    <row r="8" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="3"/>
+      <c r="B9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="3"/>
+      <c r="B11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="3"/>
+      <c r="B13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="3"/>
+      <c r="B15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="7">
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A14:A15"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
   </mergeCells>
   <conditionalFormatting sqref="B2:C3">
     <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
@@ -760,5 +880,6 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="72" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>